--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129373391</v>
       </c>
       <c r="B2" t="n">
-        <v>91507</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129373409</v>
       </c>
       <c r="B4" t="n">
-        <v>91543</v>
+        <v>91540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373407</v>
       </c>
       <c r="B5" t="n">
-        <v>91543</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129373446</v>
       </c>
       <c r="B12" t="n">
-        <v>91561</v>
+        <v>91558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129373446</v>
+        <v>129373421</v>
       </c>
       <c r="B12" t="n">
-        <v>91558</v>
+        <v>79108</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>637</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663428</v>
+        <v>663343</v>
       </c>
       <c r="R12" t="n">
-        <v>6987454</v>
+        <v>6987403</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,34 +1742,30 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129373421</v>
+        <v>129373446</v>
       </c>
       <c r="B13" t="n">
-        <v>79108</v>
+        <v>91560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>637</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1777,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663343</v>
+        <v>663428</v>
       </c>
       <c r="R13" t="n">
-        <v>6987403</v>
+        <v>6987454</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,7 +1835,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373452</v>
+        <v>129373461</v>
       </c>
       <c r="B14" t="n">
         <v>79041</v>
@@ -1874,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663412</v>
+        <v>663382</v>
       </c>
       <c r="R14" t="n">
-        <v>6987467</v>
+        <v>6987446</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1904,12 +1900,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1936,7 +1932,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373461</v>
+        <v>129373452</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -1971,10 +1967,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663382</v>
+        <v>663412</v>
       </c>
       <c r="R15" t="n">
-        <v>6987446</v>
+        <v>6987467</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2001,12 +1997,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129373450</v>
+        <v>129373451</v>
       </c>
       <c r="B9" t="n">
         <v>79041</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>663391</v>
+        <v>663402</v>
       </c>
       <c r="R9" t="n">
-        <v>6987492</v>
+        <v>6987485</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129373451</v>
+        <v>129373450</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>663402</v>
+        <v>663391</v>
       </c>
       <c r="R10" t="n">
-        <v>6987485</v>
+        <v>6987492</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,34 +1645,30 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129373421</v>
+        <v>129373446</v>
       </c>
       <c r="B12" t="n">
-        <v>79108</v>
+        <v>91560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>637</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1680,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663343</v>
+        <v>663428</v>
       </c>
       <c r="R12" t="n">
-        <v>6987403</v>
+        <v>6987454</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,30 +1738,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129373446</v>
+        <v>129373421</v>
       </c>
       <c r="B13" t="n">
-        <v>91560</v>
+        <v>79108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>637</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663428</v>
+        <v>663343</v>
       </c>
       <c r="R13" t="n">
-        <v>6987454</v>
+        <v>6987403</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373461</v>
+        <v>129373452</v>
       </c>
       <c r="B14" t="n">
         <v>79041</v>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663382</v>
+        <v>663412</v>
       </c>
       <c r="R14" t="n">
-        <v>6987446</v>
+        <v>6987467</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1900,12 +1900,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1932,7 +1932,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373452</v>
+        <v>129373461</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663412</v>
+        <v>663382</v>
       </c>
       <c r="R15" t="n">
-        <v>6987467</v>
+        <v>6987446</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129373391</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129373419</v>
       </c>
       <c r="B3" t="n">
-        <v>79108</v>
+        <v>79110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129373409</v>
       </c>
       <c r="B4" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373407</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373387</v>
       </c>
       <c r="B6" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129373454</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129373420</v>
       </c>
       <c r="B8" t="n">
-        <v>79108</v>
+        <v>79110</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129373451</v>
+        <v>129373450</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>663402</v>
+        <v>663391</v>
       </c>
       <c r="R9" t="n">
-        <v>6987485</v>
+        <v>6987492</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129373450</v>
+        <v>129373451</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>663391</v>
+        <v>663402</v>
       </c>
       <c r="R10" t="n">
-        <v>6987492</v>
+        <v>6987485</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>129373453</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129373446</v>
       </c>
       <c r="B12" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129373421</v>
       </c>
       <c r="B13" t="n">
-        <v>79108</v>
+        <v>79110</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>129373452</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>129373461</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>129373448</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>129373413</v>
       </c>
       <c r="B17" t="n">
-        <v>79108</v>
+        <v>79110</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -1645,30 +1645,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129373446</v>
+        <v>129373421</v>
       </c>
       <c r="B12" t="n">
-        <v>91563</v>
+        <v>79110</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>637</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1676,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663428</v>
+        <v>663343</v>
       </c>
       <c r="R12" t="n">
-        <v>6987454</v>
+        <v>6987403</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1738,34 +1742,30 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129373421</v>
+        <v>129373446</v>
       </c>
       <c r="B13" t="n">
-        <v>79110</v>
+        <v>91563</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>637</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663343</v>
+        <v>663428</v>
       </c>
       <c r="R13" t="n">
-        <v>6987403</v>
+        <v>6987454</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129373391</v>
       </c>
       <c r="B2" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129373419</v>
       </c>
       <c r="B3" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129373409</v>
       </c>
       <c r="B4" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373407</v>
       </c>
       <c r="B5" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373387</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129373454</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129373420</v>
       </c>
       <c r="B8" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129373450</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129373451</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129373453</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129373421</v>
       </c>
       <c r="B12" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129373446</v>
       </c>
       <c r="B13" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>129373452</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>129373461</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>129373448</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>129373413</v>
       </c>
       <c r="B17" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129373391</v>
       </c>
       <c r="B2" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129373409</v>
       </c>
       <c r="B4" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373407</v>
       </c>
       <c r="B5" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129373446</v>
       </c>
       <c r="B13" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129373391</v>
       </c>
       <c r="B2" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129373409</v>
       </c>
       <c r="B4" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373407</v>
       </c>
       <c r="B5" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129373446</v>
       </c>
       <c r="B13" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -1645,34 +1645,30 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129373421</v>
+        <v>129373446</v>
       </c>
       <c r="B12" t="n">
-        <v>79111</v>
+        <v>91570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>637</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1680,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663343</v>
+        <v>663428</v>
       </c>
       <c r="R12" t="n">
-        <v>6987403</v>
+        <v>6987454</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,30 +1738,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129373446</v>
+        <v>129373421</v>
       </c>
       <c r="B13" t="n">
-        <v>91570</v>
+        <v>79111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>637</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663428</v>
+        <v>663343</v>
       </c>
       <c r="R13" t="n">
-        <v>6987454</v>
+        <v>6987403</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129373391</v>
       </c>
       <c r="B2" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129373409</v>
       </c>
       <c r="B4" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373407</v>
       </c>
       <c r="B5" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129373450</v>
+        <v>129373451</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>663391</v>
+        <v>663402</v>
       </c>
       <c r="R9" t="n">
-        <v>6987492</v>
+        <v>6987485</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129373451</v>
+        <v>129373450</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>663402</v>
+        <v>663391</v>
       </c>
       <c r="R10" t="n">
-        <v>6987485</v>
+        <v>6987492</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>129373446</v>
       </c>
       <c r="B12" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129373451</v>
+        <v>129373450</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>663402</v>
+        <v>663391</v>
       </c>
       <c r="R9" t="n">
-        <v>6987485</v>
+        <v>6987492</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129373450</v>
+        <v>129373451</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>663391</v>
+        <v>663402</v>
       </c>
       <c r="R10" t="n">
-        <v>6987492</v>
+        <v>6987485</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -1645,30 +1645,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129373446</v>
+        <v>129373421</v>
       </c>
       <c r="B12" t="n">
-        <v>91573</v>
+        <v>79111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>637</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1676,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663428</v>
+        <v>663343</v>
       </c>
       <c r="R12" t="n">
-        <v>6987454</v>
+        <v>6987403</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1738,34 +1742,30 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129373421</v>
+        <v>129373446</v>
       </c>
       <c r="B13" t="n">
-        <v>79111</v>
+        <v>91573</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>637</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663343</v>
+        <v>663428</v>
       </c>
       <c r="R13" t="n">
-        <v>6987403</v>
+        <v>6987454</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129373450</v>
+        <v>129373451</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>663391</v>
+        <v>663402</v>
       </c>
       <c r="R9" t="n">
-        <v>6987492</v>
+        <v>6987485</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129373451</v>
+        <v>129373450</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>663402</v>
+        <v>663391</v>
       </c>
       <c r="R10" t="n">
-        <v>6987485</v>
+        <v>6987492</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129373451</v>
+        <v>129373450</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>663402</v>
+        <v>663391</v>
       </c>
       <c r="R9" t="n">
-        <v>6987485</v>
+        <v>6987492</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129373450</v>
+        <v>129373451</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>663391</v>
+        <v>663402</v>
       </c>
       <c r="R10" t="n">
-        <v>6987492</v>
+        <v>6987485</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,34 +1645,30 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129373421</v>
+        <v>129373446</v>
       </c>
       <c r="B12" t="n">
-        <v>79111</v>
+        <v>91573</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>637</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1680,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663343</v>
+        <v>663428</v>
       </c>
       <c r="R12" t="n">
-        <v>6987403</v>
+        <v>6987454</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,30 +1738,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129373446</v>
+        <v>129373421</v>
       </c>
       <c r="B13" t="n">
-        <v>91573</v>
+        <v>79111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>637</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663428</v>
+        <v>663343</v>
       </c>
       <c r="R13" t="n">
-        <v>6987454</v>
+        <v>6987403</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129373391</v>
       </c>
       <c r="B2" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129373419</v>
       </c>
       <c r="B3" t="n">
-        <v>79111</v>
+        <v>79137</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129373409</v>
       </c>
       <c r="B4" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373407</v>
       </c>
       <c r="B5" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373387</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129373454</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129373420</v>
       </c>
       <c r="B8" t="n">
-        <v>79111</v>
+        <v>79137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129373450</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129373451</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129373453</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,34 +1645,30 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129373421</v>
+        <v>129373446</v>
       </c>
       <c r="B12" t="n">
-        <v>79111</v>
+        <v>91601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>637</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1680,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663343</v>
+        <v>663428</v>
       </c>
       <c r="R12" t="n">
-        <v>6987403</v>
+        <v>6987454</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,30 +1738,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129373446</v>
+        <v>129373421</v>
       </c>
       <c r="B13" t="n">
-        <v>91573</v>
+        <v>79137</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>637</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663428</v>
+        <v>663343</v>
       </c>
       <c r="R13" t="n">
-        <v>6987454</v>
+        <v>6987403</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1838,7 +1838,7 @@
         <v>129373452</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>129373461</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>129373448</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>129373413</v>
       </c>
       <c r="B17" t="n">
-        <v>79111</v>
+        <v>79137</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -1645,30 +1645,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129373446</v>
+        <v>129373421</v>
       </c>
       <c r="B12" t="n">
-        <v>91601</v>
+        <v>79137</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>637</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1676,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663428</v>
+        <v>663343</v>
       </c>
       <c r="R12" t="n">
-        <v>6987454</v>
+        <v>6987403</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1738,34 +1742,30 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129373421</v>
+        <v>129373446</v>
       </c>
       <c r="B13" t="n">
-        <v>79137</v>
+        <v>91601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>637</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663343</v>
+        <v>663428</v>
       </c>
       <c r="R13" t="n">
-        <v>6987403</v>
+        <v>6987454</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129373391</v>
       </c>
       <c r="B2" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129373419</v>
       </c>
       <c r="B3" t="n">
-        <v>79137</v>
+        <v>79142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129373409</v>
       </c>
       <c r="B4" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373407</v>
       </c>
       <c r="B5" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373387</v>
       </c>
       <c r="B6" t="n">
-        <v>79102</v>
+        <v>79107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129373454</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129373420</v>
       </c>
       <c r="B8" t="n">
-        <v>79137</v>
+        <v>79142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129373450</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129373451</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129373453</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129373421</v>
       </c>
       <c r="B12" t="n">
-        <v>79137</v>
+        <v>79142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129373446</v>
       </c>
       <c r="B13" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>129373452</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>129373461</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>129373448</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>129373413</v>
       </c>
       <c r="B17" t="n">
-        <v>79137</v>
+        <v>79142</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129373391</v>
       </c>
       <c r="B2" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129373419</v>
       </c>
       <c r="B3" t="n">
-        <v>79142</v>
+        <v>79143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129373409</v>
       </c>
       <c r="B4" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373407</v>
       </c>
       <c r="B5" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373387</v>
       </c>
       <c r="B6" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129373454</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129373420</v>
       </c>
       <c r="B8" t="n">
-        <v>79142</v>
+        <v>79143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129373450</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129373451</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129373453</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,34 +1645,30 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129373421</v>
+        <v>129373446</v>
       </c>
       <c r="B12" t="n">
-        <v>79142</v>
+        <v>91608</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>637</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1680,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663343</v>
+        <v>663428</v>
       </c>
       <c r="R12" t="n">
-        <v>6987403</v>
+        <v>6987454</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,30 +1738,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129373446</v>
+        <v>129373421</v>
       </c>
       <c r="B13" t="n">
-        <v>91607</v>
+        <v>79143</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>637</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663428</v>
+        <v>663343</v>
       </c>
       <c r="R13" t="n">
-        <v>6987454</v>
+        <v>6987403</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1838,7 +1838,7 @@
         <v>129373452</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>129373461</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>129373448</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>129373413</v>
       </c>
       <c r="B17" t="n">
-        <v>79142</v>
+        <v>79143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129373391</v>
       </c>
       <c r="B2" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129373419</v>
       </c>
       <c r="B3" t="n">
-        <v>79143</v>
+        <v>79148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129373409</v>
       </c>
       <c r="B4" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373407</v>
       </c>
       <c r="B5" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373387</v>
       </c>
       <c r="B6" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129373454</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129373420</v>
       </c>
       <c r="B8" t="n">
-        <v>79143</v>
+        <v>79148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129373450</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129373451</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129373453</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,30 +1645,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129373446</v>
+        <v>129373421</v>
       </c>
       <c r="B12" t="n">
-        <v>91608</v>
+        <v>79148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>637</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1676,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663428</v>
+        <v>663343</v>
       </c>
       <c r="R12" t="n">
-        <v>6987454</v>
+        <v>6987403</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1738,34 +1742,30 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129373421</v>
+        <v>129373446</v>
       </c>
       <c r="B13" t="n">
-        <v>79143</v>
+        <v>91613</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>637</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663343</v>
+        <v>663428</v>
       </c>
       <c r="R13" t="n">
-        <v>6987403</v>
+        <v>6987454</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1838,7 +1838,7 @@
         <v>129373452</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>129373461</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>129373448</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>129373413</v>
       </c>
       <c r="B17" t="n">
-        <v>79143</v>
+        <v>79148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -1645,34 +1645,30 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129373421</v>
+        <v>129373446</v>
       </c>
       <c r="B12" t="n">
-        <v>79148</v>
+        <v>91613</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>637</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1680,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663343</v>
+        <v>663428</v>
       </c>
       <c r="R12" t="n">
-        <v>6987403</v>
+        <v>6987454</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,30 +1738,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129373446</v>
+        <v>129373421</v>
       </c>
       <c r="B13" t="n">
-        <v>91613</v>
+        <v>79148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>637</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663428</v>
+        <v>663343</v>
       </c>
       <c r="R13" t="n">
-        <v>6987454</v>
+        <v>6987403</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373452</v>
+        <v>129373461</v>
       </c>
       <c r="B14" t="n">
         <v>79081</v>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663412</v>
+        <v>663382</v>
       </c>
       <c r="R14" t="n">
-        <v>6987467</v>
+        <v>6987446</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1900,12 +1900,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1932,7 +1932,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373461</v>
+        <v>129373452</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663382</v>
+        <v>663412</v>
       </c>
       <c r="R15" t="n">
-        <v>6987446</v>
+        <v>6987467</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 45606-2025 artfynd.xlsx
+++ b/artfynd/A 45606-2025 artfynd.xlsx
@@ -1835,7 +1835,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373461</v>
+        <v>129373452</v>
       </c>
       <c r="B14" t="n">
         <v>79081</v>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663382</v>
+        <v>663412</v>
       </c>
       <c r="R14" t="n">
-        <v>6987446</v>
+        <v>6987467</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1900,12 +1900,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1932,7 +1932,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373452</v>
+        <v>129373461</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663412</v>
+        <v>663382</v>
       </c>
       <c r="R15" t="n">
-        <v>6987467</v>
+        <v>6987446</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
